--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
@@ -20,6 +20,10 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report(空白)'!$B$2:$AA$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Report(範本)'!$B$2:$AA$64</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4012,7 +4016,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="工作表1"/>
+  <sheetPr codeName="工作表1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:BR67"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
@@ -6136,14 +6142,18 @@
     <mergeCell ref="X10:Z10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C07CF2-022B-45F5-BE30-2881F0C24896}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:BR67"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
@@ -8407,8 +8417,9 @@
     <mergeCell ref="Y65:AA65"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
@@ -21,8 +21,8 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report(空白)'!$B$2:$AA$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Report(範本)'!$B$2:$AA$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report(空白)'!$B$2:$AA$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Report(範本)'!$B$2:$AA$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
@@ -684,24 +684,26 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
+            <a:defRPr sz="1200"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:rPr>
             <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-            <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+            <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -709,7 +711,7 @@
             <a:lnSpc>
               <a:spcPts val="2000"/>
             </a:lnSpc>
-            <a:defRPr sz="1000"/>
+            <a:defRPr sz="1200"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -717,11 +719,19 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:t>New-Fast Technology Co., LTD</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l" rtl="0">
@@ -902,24 +912,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -927,7 +939,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -935,11 +947,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1065,24 +1085,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1090,7 +1112,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1098,11 +1120,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1228,24 +1258,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1253,7 +1285,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1261,28 +1293,18 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
-              <a:t>New-Fast Technology Co., LT</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
-              </a:rPr>
-              <a:t>D</a:t>
+              <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1409,24 +1431,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1434,7 +1458,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1442,11 +1466,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1572,24 +1604,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1597,7 +1631,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1605,11 +1639,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1735,24 +1777,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1760,7 +1804,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1768,11 +1812,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1898,24 +1950,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1923,7 +1977,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1931,11 +1985,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2061,24 +2123,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2086,7 +2150,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2094,11 +2158,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2169,24 +2241,26 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
+            <a:defRPr sz="1200"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:rPr>
             <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-            <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+            <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2194,7 +2268,7 @@
             <a:lnSpc>
               <a:spcPts val="2000"/>
             </a:lnSpc>
-            <a:defRPr sz="1000"/>
+            <a:defRPr sz="1200"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2202,11 +2276,19 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:t>New-Fast Technology Co., LTD</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l" rtl="0">
@@ -2387,24 +2469,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2412,7 +2496,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2420,11 +2504,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2550,24 +2642,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2575,7 +2669,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2583,11 +2677,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2713,24 +2815,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2738,7 +2842,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2746,28 +2850,18 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
-              <a:t>New-Fast Technology Co., LT</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
-              </a:rPr>
-              <a:t>D</a:t>
+              <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2894,24 +2988,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2919,7 +3015,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2927,11 +3023,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3057,24 +3161,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3082,7 +3188,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3090,11 +3196,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3220,24 +3334,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3245,7 +3361,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3253,11 +3369,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3383,24 +3507,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3408,7 +3534,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3416,11 +3542,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3546,24 +3680,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
-              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3571,7 +3707,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1000"/>
+              <a:defRPr sz="1200"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3579,11 +3715,19 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">

--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
@@ -20,10 +20,6 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report(空白)'!$B$2:$AA$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Report(範本)'!$B$2:$AA$66</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -684,26 +680,24 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1200"/>
+            <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:rPr>
             <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-            <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-            <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+            <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -711,7 +705,7 @@
             <a:lnSpc>
               <a:spcPts val="2000"/>
             </a:lnSpc>
-            <a:defRPr sz="1200"/>
+            <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -719,19 +713,11 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:t>New-Fast Technology Co., LTD</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l" rtl="0">
@@ -912,26 +898,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -939,7 +923,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -947,19 +931,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1085,26 +1061,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1112,7 +1086,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1120,19 +1094,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1258,26 +1224,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1285,7 +1249,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1293,18 +1257,28 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
-              <a:t>New-Fast Technology Co., LTD</a:t>
+              <a:t>New-Fast Technology Co., LT</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              </a:rPr>
+              <a:t>D</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:cs typeface="Times New Roman"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1431,26 +1405,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1458,7 +1430,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1466,19 +1438,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1604,26 +1568,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1631,7 +1593,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1639,19 +1601,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1777,26 +1731,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1804,7 +1756,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1812,19 +1764,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -1950,26 +1894,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -1977,7 +1919,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -1985,19 +1927,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2123,26 +2057,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2150,7 +2082,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2158,19 +2090,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2241,26 +2165,24 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1200"/>
+            <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:rPr>
             <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-            <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-            <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+            <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+            <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2268,7 +2190,7 @@
             <a:lnSpc>
               <a:spcPts val="2000"/>
             </a:lnSpc>
-            <a:defRPr sz="1200"/>
+            <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2276,19 +2198,11 @@
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:t>New-Fast Technology Co., LTD</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l" rtl="0">
@@ -2469,26 +2383,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2496,7 +2408,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2504,19 +2416,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2642,26 +2546,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2669,7 +2571,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2677,19 +2579,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -2815,26 +2709,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2842,7 +2734,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -2850,18 +2742,28 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
-              <a:t>New-Fast Technology Co., LTD</a:t>
+              <a:t>New-Fast Technology Co., LT</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              </a:rPr>
+              <a:t>D</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:cs typeface="Times New Roman"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -2988,26 +2890,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3015,7 +2915,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3023,19 +2923,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3161,26 +3053,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3188,7 +3078,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3196,19 +3086,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3334,26 +3216,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3361,7 +3241,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3369,19 +3249,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3507,26 +3379,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3534,7 +3404,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3542,19 +3412,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -3680,26 +3542,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-                <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+                <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
               </a:rPr>
               <a:t>金 兆 益 科 技 股 份 有 限 公 司</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
+            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="-100" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:ea typeface="MingLiU" pitchFamily="54" charset="136"/>
-              <a:cs typeface="MingLiU" pitchFamily="54" charset="136"/>
+              <a:latin typeface="標楷體" pitchFamily="65" charset="-120"/>
+              <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
             </a:endParaRPr>
           </a:p>
           <a:p>
@@ -3707,7 +3567,7 @@
               <a:lnSpc>
                 <a:spcPts val="2000"/>
               </a:lnSpc>
-              <a:defRPr sz="1200"/>
+              <a:defRPr sz="1000"/>
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
@@ -3715,19 +3575,11 @@
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="標楷體" pitchFamily="65" charset="-120"/>
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:rPr>
               <a:t>New-Fast Technology Co., LTD</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1200" b="1" i="0" u="none" strike="noStrike" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
           </a:p>
           <a:p>
             <a:pPr algn="l" rtl="0">
@@ -4160,9 +4012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="工作表1">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+  <sheetPr codeName="工作表1"/>
   <dimension ref="A1:BR67"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
@@ -6286,18 +6136,14 @@
     <mergeCell ref="X10:Z10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C07CF2-022B-45F5-BE30-2881F0C24896}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:BR67"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
@@ -8561,9 +8407,8 @@
     <mergeCell ref="Y65:AA65"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(小卡).xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://newfastsemi-my.sharepoint.com/personal/becky_chen_newfast-semi_com/Documents/Becky/資管資料/專案工作/IN PROGRESS/鋼瓶生產/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rdpuser\RiderProjects\JinZhaoYi-GasCylinder-QC-DataLoader\src\JinZhaoYi.GasQcDataLoader\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="35" documentId="8_{FCA60125-DA94-43DE-A67E-BD609FF73851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F01C3A5-D9EB-4FFC-AFF5-91742A950E98}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report(空白)" sheetId="2" r:id="rId1"/>
@@ -558,32 +558,32 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -817,8 +817,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="85719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="87624"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -980,8 +980,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="85719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="87624"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1143,8 +1143,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="108585" y="4657719"/>
-          <a:ext cx="2720340" cy="577221"/>
+          <a:off x="114300" y="4735824"/>
+          <a:ext cx="3009900" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1324,8 +1324,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="4657719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="4735824"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1487,8 +1487,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="4657719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="4735824"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1650,8 +1650,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="108585" y="9222099"/>
-          <a:ext cx="2720340" cy="577221"/>
+          <a:off x="114300" y="9374499"/>
+          <a:ext cx="3009900" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1813,8 +1813,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="9222099"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="9374499"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -1976,8 +1976,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="9222099"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="9374499"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -2302,8 +2302,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="85719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="87624"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -2465,8 +2465,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="85719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="87624"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -2628,8 +2628,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="108585" y="4657719"/>
-          <a:ext cx="2720340" cy="577221"/>
+          <a:off x="114300" y="4735824"/>
+          <a:ext cx="3040380" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -2809,8 +2809,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="4657719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="4735824"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -2972,8 +2972,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="4657719"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="4735824"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -3135,8 +3135,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="108585" y="9222099"/>
-          <a:ext cx="2720340" cy="577221"/>
+          <a:off x="114300" y="9374499"/>
+          <a:ext cx="3040380" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -3298,8 +3298,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2935605" y="9222099"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="3267075" y="9374499"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -3461,8 +3461,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5747385" y="9222099"/>
-          <a:ext cx="2703195" cy="577221"/>
+          <a:off x="6400800" y="9374499"/>
+          <a:ext cx="3019425" cy="588651"/>
           <a:chOff x="47625" y="8755374"/>
           <a:chExt cx="3028950" cy="588651"/>
         </a:xfrm>
@@ -4014,33 +4014,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
   <dimension ref="A1:BR67"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="0.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="2.6640625" customWidth="1"/>
-    <col min="4" max="4" width="2.33203125" customWidth="1"/>
-    <col min="5" max="5" width="1.21875" customWidth="1"/>
-    <col min="6" max="6" width="2.44140625" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" customWidth="1"/>
-    <col min="9" max="9" width="3.44140625" customWidth="1"/>
-    <col min="10" max="10" width="0.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" customWidth="1"/>
-    <col min="14" max="14" width="1.21875" customWidth="1"/>
-    <col min="15" max="15" width="2.44140625" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" customWidth="1"/>
-    <col min="18" max="18" width="3.21875" customWidth="1"/>
-    <col min="19" max="19" width="0.88671875" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" customWidth="1"/>
-    <col min="21" max="21" width="2.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.33203125" customWidth="1"/>
-    <col min="23" max="23" width="1.21875" customWidth="1"/>
-    <col min="24" max="24" width="2.44140625" customWidth="1"/>
-    <col min="26" max="26" width="4.6640625" customWidth="1"/>
-    <col min="27" max="27" width="3.21875" customWidth="1"/>
-    <col min="32" max="32" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.875" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="2.625" customWidth="1"/>
+    <col min="4" max="4" width="2.375" customWidth="1"/>
+    <col min="5" max="5" width="1.25" customWidth="1"/>
+    <col min="6" max="6" width="2.5" customWidth="1"/>
+    <col min="8" max="8" width="4.625" customWidth="1"/>
+    <col min="9" max="9" width="3.5" customWidth="1"/>
+    <col min="10" max="10" width="0.875" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="2.625" customWidth="1"/>
+    <col min="13" max="13" width="2.375" customWidth="1"/>
+    <col min="14" max="14" width="1.25" customWidth="1"/>
+    <col min="15" max="15" width="2.5" customWidth="1"/>
+    <col min="17" max="17" width="4.625" customWidth="1"/>
+    <col min="18" max="18" width="3.25" customWidth="1"/>
+    <col min="19" max="19" width="0.875" customWidth="1"/>
+    <col min="20" max="20" width="14.625" customWidth="1"/>
+    <col min="21" max="21" width="2.625" customWidth="1"/>
+    <col min="22" max="22" width="2.375" customWidth="1"/>
+    <col min="23" max="23" width="1.25" customWidth="1"/>
+    <col min="24" max="24" width="2.5" customWidth="1"/>
+    <col min="26" max="26" width="4.625" customWidth="1"/>
+    <col min="27" max="27" width="3.25" customWidth="1"/>
+    <col min="32" max="32" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="3.75" customHeight="1">
@@ -4064,25 +4064,25 @@
         <v>13</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
       <c r="K6" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L6" s="9"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
       <c r="T6" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U6" s="9"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="18"/>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="1" t="s">
@@ -4134,9 +4134,9 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="7" t="str">
@@ -4146,9 +4146,9 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
       <c r="R8" s="3"/>
       <c r="T8" s="7" t="str">
         <f>$B$8</f>
@@ -4157,9 +4157,9 @@
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:32" ht="22.5" customHeight="1">
@@ -4169,9 +4169,9 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="7" t="str">
@@ -4181,9 +4181,9 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
       <c r="R9" s="3"/>
       <c r="T9" s="7" t="str">
         <f>$B$9</f>
@@ -4192,9 +4192,9 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:32" ht="22.5" customHeight="1">
@@ -4204,9 +4204,9 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="7" t="str">
@@ -4216,9 +4216,9 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
       <c r="R10" s="3"/>
       <c r="T10" s="7" t="str">
         <f>$B$10</f>
@@ -4227,9 +4227,9 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
       <c r="AA10" s="3"/>
     </row>
     <row r="11" spans="1:32" ht="22.5" customHeight="1">
@@ -4239,9 +4239,9 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="7" t="str">
@@ -4251,9 +4251,9 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
       <c r="R11" s="3"/>
       <c r="T11" s="7" t="str">
         <f>$B$11</f>
@@ -4262,9 +4262,9 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:32" ht="22.5" customHeight="1">
@@ -4274,9 +4274,9 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="7" t="str">
@@ -4286,9 +4286,9 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
       <c r="R12" s="3"/>
       <c r="T12" s="7" t="str">
         <f>$B$12</f>
@@ -4297,9 +4297,9 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
       <c r="AA12" s="3"/>
     </row>
     <row r="13" spans="1:32" ht="22.5" customHeight="1">
@@ -4309,9 +4309,9 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="7" t="str">
@@ -4321,9 +4321,9 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
       <c r="R13" s="3"/>
       <c r="T13" s="7" t="str">
         <f>$B$13</f>
@@ -4332,9 +4332,9 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:32" ht="22.5" customHeight="1">
@@ -4344,9 +4344,9 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="7" t="str">
@@ -4356,9 +4356,9 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
       <c r="R14" s="3"/>
       <c r="T14" s="7" t="str">
         <f>$B$14</f>
@@ -4367,9 +4367,9 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
       <c r="AA14" s="3"/>
       <c r="AF14" s="11"/>
     </row>
@@ -4380,9 +4380,9 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="7" t="str">
@@ -4392,9 +4392,9 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
       <c r="R15" s="3"/>
       <c r="T15" s="7" t="str">
         <f>$B$15</f>
@@ -4403,9 +4403,9 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:32" ht="22.5" customHeight="1">
@@ -4415,9 +4415,9 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="7" t="str">
@@ -4427,9 +4427,9 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
       <c r="R16" s="3"/>
       <c r="T16" s="7" t="str">
         <f>$B$16</f>
@@ -4438,9 +4438,9 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:28" ht="7.5" customHeight="1">
@@ -4504,12 +4504,12 @@
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="3"/>
       <c r="K19" s="20" t="s">
         <v>18</v>
@@ -4517,54 +4517,54 @@
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
-      <c r="O19" s="21" t="s">
+      <c r="O19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
       <c r="T19" s="20" t="s">
         <v>18</v>
       </c>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
-      <c r="X19" s="21" t="s">
+      <c r="X19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:28" ht="16.5" customHeight="1">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
-      <c r="T20" s="18" t="s">
+      <c r="T20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
       <c r="AA20" s="3"/>
@@ -4574,62 +4574,62 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="O21" s="6"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="X21" s="6"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="F22" s="17" t="s">
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="F22" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="K22" s="16" t="str">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="K22" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="O22" s="17" t="str">
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="O22" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="T22" s="16" t="str">
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="T22" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="X22" s="17" t="str">
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="X22" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
     </row>
     <row r="23" spans="1:28" ht="3.75" customHeight="1">
       <c r="A23" t="s">
@@ -4653,25 +4653,25 @@
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="C28" s="9"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
       <c r="K28" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L28" s="9"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
       <c r="T28" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U28" s="9"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
     </row>
     <row r="29" spans="1:28">
       <c r="B29" s="1" t="str">
@@ -4726,9 +4726,9 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="7" t="str">
@@ -4738,9 +4738,9 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
       <c r="R30" s="3"/>
       <c r="T30" s="7" t="str">
         <f>$B$8</f>
@@ -4749,9 +4749,9 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
-      <c r="X30" s="22"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
+      <c r="X30" s="21"/>
+      <c r="Y30" s="21"/>
+      <c r="Z30" s="21"/>
       <c r="AA30" s="3"/>
     </row>
     <row r="31" spans="1:28" ht="22.5" customHeight="1">
@@ -4762,9 +4762,9 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="7" t="str">
@@ -4774,9 +4774,9 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
       <c r="R31" s="3"/>
       <c r="T31" s="7" t="str">
         <f>$B$9</f>
@@ -4785,9 +4785,9 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
-      <c r="X31" s="22"/>
-      <c r="Y31" s="22"/>
-      <c r="Z31" s="22"/>
+      <c r="X31" s="21"/>
+      <c r="Y31" s="21"/>
+      <c r="Z31" s="21"/>
       <c r="AA31" s="3"/>
       <c r="AB31" t="s">
         <v>14</v>
@@ -4801,9 +4801,9 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="7" t="str">
@@ -4813,9 +4813,9 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
       <c r="R32" s="3"/>
       <c r="T32" s="7" t="str">
         <f>$B$10</f>
@@ -4824,9 +4824,9 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
+      <c r="X32" s="21"/>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="21"/>
       <c r="AA32" s="3"/>
     </row>
     <row r="33" spans="1:70" ht="22.5" customHeight="1">
@@ -4837,9 +4837,9 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="7" t="str">
@@ -4849,9 +4849,9 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
       <c r="R33" s="3"/>
       <c r="T33" s="7" t="str">
         <f>$B$11</f>
@@ -4860,9 +4860,9 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
-      <c r="X33" s="22"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="22"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
       <c r="AA33" s="3"/>
     </row>
     <row r="34" spans="1:70" ht="22.5" customHeight="1">
@@ -4873,9 +4873,9 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="7" t="str">
@@ -4885,9 +4885,9 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
       <c r="R34" s="3"/>
       <c r="T34" s="7" t="str">
         <f>$B$12</f>
@@ -4896,9 +4896,9 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
+      <c r="X34" s="21"/>
+      <c r="Y34" s="21"/>
+      <c r="Z34" s="21"/>
       <c r="AA34" s="3"/>
       <c r="AF34" s="12"/>
       <c r="AG34" s="13"/>
@@ -4948,9 +4948,9 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="7" t="str">
@@ -4960,9 +4960,9 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
       <c r="R35" s="3"/>
       <c r="T35" s="7" t="str">
         <f>$B$13</f>
@@ -4971,9 +4971,9 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
+      <c r="X35" s="21"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="21"/>
       <c r="AA35" s="3"/>
       <c r="AF35" s="12"/>
       <c r="AG35" s="13"/>
@@ -5023,9 +5023,9 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="7" t="str">
@@ -5035,9 +5035,9 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
       <c r="R36" s="3"/>
       <c r="T36" s="7" t="str">
         <f>$B$14</f>
@@ -5046,9 +5046,9 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
+      <c r="X36" s="21"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
       <c r="AA36" s="3"/>
     </row>
     <row r="37" spans="1:70" ht="22.5" customHeight="1">
@@ -5059,9 +5059,9 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="7" t="str">
@@ -5071,9 +5071,9 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="21"/>
       <c r="R37" s="3"/>
       <c r="T37" s="7" t="str">
         <f>$B$15</f>
@@ -5082,9 +5082,9 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
-      <c r="X37" s="22"/>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="22"/>
+      <c r="X37" s="21"/>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="21"/>
       <c r="AA37" s="3"/>
     </row>
     <row r="38" spans="1:70" ht="22.5" customHeight="1">
@@ -5095,9 +5095,9 @@
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="7" t="str">
@@ -5107,9 +5107,9 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
       <c r="R38" s="3"/>
       <c r="T38" s="7" t="str">
         <f>$B$16</f>
@@ -5118,9 +5118,9 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
+      <c r="X38" s="21"/>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="21"/>
       <c r="AA38" s="3"/>
     </row>
     <row r="39" spans="1:70" ht="7.5" customHeight="1">
@@ -5184,12 +5184,12 @@
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
       <c r="J41" s="3"/>
       <c r="K41" s="20" t="s">
         <v>17</v>
@@ -5197,54 +5197,54 @@
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
-      <c r="O41" s="21" t="s">
+      <c r="O41" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="21"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
       <c r="T41" s="20" t="s">
         <v>17</v>
       </c>
       <c r="U41" s="20"/>
       <c r="V41" s="20"/>
       <c r="W41" s="20"/>
-      <c r="X41" s="21" t="s">
+      <c r="X41" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Y41" s="21"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="21"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="19"/>
     </row>
     <row r="42" spans="1:70" ht="16.5" customHeight="1">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="3"/>
-      <c r="T42" s="18" t="s">
+      <c r="T42" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="22"/>
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
       <c r="AA42" s="3"/>
@@ -5254,64 +5254,64 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="F43" s="6"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="O43" s="6"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
       <c r="T43" s="6"/>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="X43" s="6"/>
-      <c r="Y43" s="19"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43" s="19"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
     </row>
     <row r="44" spans="1:70">
-      <c r="B44" s="16" t="str">
+      <c r="B44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="F44" s="17" t="str">
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="F44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="K44" s="16" t="str">
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="K44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="O44" s="17" t="str">
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="O44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="T44" s="16" t="str">
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="T44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="X44" s="17" t="str">
+      <c r="U44" s="23"/>
+      <c r="V44" s="23"/>
+      <c r="X44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
-      <c r="AA44" s="17"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
     </row>
     <row r="45" spans="1:70" ht="3" customHeight="1">
       <c r="A45" t="s">
@@ -5335,31 +5335,31 @@
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="C50" s="9"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
       <c r="K50" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L50" s="9"/>
-      <c r="O50" s="19" t="e">
+      <c r="O50" s="18" t="e">
         <f ca="1">IF(OFFSET(#REF!,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),0)="","",OFFSET(#REF!,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),0))</f>
         <v>#REF!</v>
       </c>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
       <c r="T50" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U50" s="9"/>
-      <c r="X50" s="19" t="e">
+      <c r="X50" s="18" t="e">
         <f ca="1">IF(OFFSET(#REF!,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),0)="","",OFFSET(#REF!,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),0))</f>
         <v>#REF!</v>
       </c>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="19"/>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="18"/>
     </row>
     <row r="51" spans="2:27">
       <c r="B51" s="1" t="str">
@@ -5414,9 +5414,9 @@
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="7" t="str">
@@ -5426,12 +5426,12 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
-      <c r="O52" s="22" t="str">
+      <c r="O52" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P49)/22)*3)+((COLUMN(P49)+2)/9),MATCH(RIGHT(K52,LEN(K52)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P49)/22)*3)+((COLUMN(P49)+2)/9),MATCH(RIGHT(K52,LEN(K52)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
+      <c r="P52" s="21"/>
+      <c r="Q52" s="21"/>
       <c r="R52" s="3"/>
       <c r="T52" s="7" t="str">
         <f>$B$8</f>
@@ -5440,12 +5440,12 @@
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
-      <c r="X52" s="22" t="str">
+      <c r="X52" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y49)/22)*3)+((COLUMN(Y49)+2)/9),MATCH(RIGHT(T52,LEN(T52)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y49)/22)*3)+((COLUMN(Y49)+2)/9),MATCH(RIGHT(T52,LEN(T52)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y52" s="22"/>
-      <c r="Z52" s="22"/>
+      <c r="Y52" s="21"/>
+      <c r="Z52" s="21"/>
       <c r="AA52" s="3"/>
     </row>
     <row r="53" spans="2:27" ht="22.5" customHeight="1">
@@ -5456,9 +5456,9 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="7" t="str">
@@ -5468,12 +5468,12 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-      <c r="O53" s="22" t="str">
+      <c r="O53" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),MATCH(RIGHT(K53,LEN(K53)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),MATCH(RIGHT(K53,LEN(K53)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
+      <c r="P53" s="21"/>
+      <c r="Q53" s="21"/>
       <c r="R53" s="3"/>
       <c r="T53" s="7" t="str">
         <f>$B$9</f>
@@ -5482,12 +5482,12 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
-      <c r="X53" s="22" t="str">
+      <c r="X53" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),MATCH(RIGHT(T53,LEN(T53)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),MATCH(RIGHT(T53,LEN(T53)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y53" s="22"/>
-      <c r="Z53" s="22"/>
+      <c r="Y53" s="21"/>
+      <c r="Z53" s="21"/>
       <c r="AA53" s="3"/>
     </row>
     <row r="54" spans="2:27" ht="22.5" customHeight="1">
@@ -5498,9 +5498,9 @@
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="7" t="str">
@@ -5510,12 +5510,12 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
-      <c r="O54" s="22" t="str">
+      <c r="O54" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P51)/22)*3)+((COLUMN(P51)+2)/9),MATCH(RIGHT(K54,LEN(K54)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P51)/22)*3)+((COLUMN(P51)+2)/9),MATCH(RIGHT(K54,LEN(K54)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
       <c r="R54" s="3"/>
       <c r="T54" s="7" t="str">
         <f>$B$10</f>
@@ -5524,12 +5524,12 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
-      <c r="X54" s="22" t="str">
+      <c r="X54" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y51)/22)*3)+((COLUMN(Y51)+2)/9),MATCH(RIGHT(T54,LEN(T54)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y51)/22)*3)+((COLUMN(Y51)+2)/9),MATCH(RIGHT(T54,LEN(T54)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y54" s="22"/>
-      <c r="Z54" s="22"/>
+      <c r="Y54" s="21"/>
+      <c r="Z54" s="21"/>
       <c r="AA54" s="3"/>
     </row>
     <row r="55" spans="2:27" ht="22.5" customHeight="1">
@@ -5540,9 +5540,9 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="7" t="str">
@@ -5552,12 +5552,12 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="O55" s="22" t="str">
+      <c r="O55" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P52)/22)*3)+((COLUMN(P52)+2)/9),MATCH(RIGHT(K55,LEN(K55)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P52)/22)*3)+((COLUMN(P52)+2)/9),MATCH(RIGHT(K55,LEN(K55)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
       <c r="R55" s="3"/>
       <c r="T55" s="7" t="str">
         <f>$B$11</f>
@@ -5566,12 +5566,12 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
-      <c r="X55" s="22" t="str">
+      <c r="X55" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y52)/22)*3)+((COLUMN(Y52)+2)/9),MATCH(RIGHT(T55,LEN(T55)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y52)/22)*3)+((COLUMN(Y52)+2)/9),MATCH(RIGHT(T55,LEN(T55)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y55" s="22"/>
-      <c r="Z55" s="22"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="21"/>
       <c r="AA55" s="3"/>
     </row>
     <row r="56" spans="2:27" ht="22.5" customHeight="1">
@@ -5582,9 +5582,9 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="7" t="str">
@@ -5594,12 +5594,12 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-      <c r="O56" s="22" t="str">
+      <c r="O56" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P53)/22)*3)+((COLUMN(P53)+2)/9),MATCH(RIGHT(K56,LEN(K56)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P53)/22)*3)+((COLUMN(P53)+2)/9),MATCH(RIGHT(K56,LEN(K56)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P56" s="22"/>
-      <c r="Q56" s="22"/>
+      <c r="P56" s="21"/>
+      <c r="Q56" s="21"/>
       <c r="R56" s="3"/>
       <c r="T56" s="7" t="str">
         <f>$B$12</f>
@@ -5608,12 +5608,12 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
-      <c r="X56" s="22" t="str">
+      <c r="X56" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y53)/22)*3)+((COLUMN(Y53)+2)/9),MATCH(RIGHT(T56,LEN(T56)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y53)/22)*3)+((COLUMN(Y53)+2)/9),MATCH(RIGHT(T56,LEN(T56)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y56" s="22"/>
-      <c r="Z56" s="22"/>
+      <c r="Y56" s="21"/>
+      <c r="Z56" s="21"/>
       <c r="AA56" s="3"/>
     </row>
     <row r="57" spans="2:27" ht="22.5" customHeight="1">
@@ -5624,9 +5624,9 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="7" t="str">
@@ -5636,12 +5636,12 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-      <c r="O57" s="22" t="str">
+      <c r="O57" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P54)/22)*3)+((COLUMN(P54)+2)/9),MATCH(RIGHT(K57,LEN(K57)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P54)/22)*3)+((COLUMN(P54)+2)/9),MATCH(RIGHT(K57,LEN(K57)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P57" s="22"/>
-      <c r="Q57" s="22"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="21"/>
       <c r="R57" s="3"/>
       <c r="T57" s="7" t="str">
         <f>$B$13</f>
@@ -5650,12 +5650,12 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
-      <c r="X57" s="22" t="str">
+      <c r="X57" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y54)/22)*3)+((COLUMN(Y54)+2)/9),MATCH(RIGHT(T57,LEN(T57)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y54)/22)*3)+((COLUMN(Y54)+2)/9),MATCH(RIGHT(T57,LEN(T57)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y57" s="22"/>
-      <c r="Z57" s="22"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="21"/>
       <c r="AA57" s="3"/>
     </row>
     <row r="58" spans="2:27" ht="22.5" customHeight="1">
@@ -5666,9 +5666,9 @@
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="7" t="str">
@@ -5678,12 +5678,12 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
-      <c r="O58" s="22" t="str">
+      <c r="O58" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P55)/22)*3)+((COLUMN(P55)+2)/9),MATCH(RIGHT(K58,LEN(K58)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P55)/22)*3)+((COLUMN(P55)+2)/9),MATCH(RIGHT(K58,LEN(K58)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="22"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="21"/>
       <c r="R58" s="3"/>
       <c r="T58" s="7" t="str">
         <f>$B$14</f>
@@ -5692,12 +5692,12 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
-      <c r="X58" s="22" t="str">
+      <c r="X58" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y55)/22)*3)+((COLUMN(Y55)+2)/9),MATCH(RIGHT(T58,LEN(T58)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y55)/22)*3)+((COLUMN(Y55)+2)/9),MATCH(RIGHT(T58,LEN(T58)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y58" s="22"/>
-      <c r="Z58" s="22"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="21"/>
       <c r="AA58" s="3"/>
     </row>
     <row r="59" spans="2:27" ht="22.5" customHeight="1">
@@ -5708,9 +5708,9 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="7" t="str">
@@ -5720,12 +5720,12 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="O59" s="22" t="str">
+      <c r="O59" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P56)/22)*3)+((COLUMN(P56)+2)/9),MATCH(RIGHT(K59,LEN(K59)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P56)/22)*3)+((COLUMN(P56)+2)/9),MATCH(RIGHT(K59,LEN(K59)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="22"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
       <c r="R59" s="3"/>
       <c r="T59" s="7" t="str">
         <f>$B$15</f>
@@ -5734,12 +5734,12 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
-      <c r="X59" s="22" t="str">
+      <c r="X59" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y56)/22)*3)+((COLUMN(Y56)+2)/9),MATCH(RIGHT(T59,LEN(T59)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y56)/22)*3)+((COLUMN(Y56)+2)/9),MATCH(RIGHT(T59,LEN(T59)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y59" s="22"/>
-      <c r="Z59" s="22"/>
+      <c r="Y59" s="21"/>
+      <c r="Z59" s="21"/>
       <c r="AA59" s="3"/>
     </row>
     <row r="60" spans="2:27" ht="22.5" customHeight="1">
@@ -5750,9 +5750,9 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="7" t="str">
@@ -5762,12 +5762,12 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-      <c r="O60" s="22" t="str">
+      <c r="O60" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(P57)/22)*3)+((COLUMN(P57)+2)/9),MATCH(RIGHT(K60,LEN(K60)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(P57)/22)*3)+((COLUMN(P57)+2)/9),MATCH(RIGHT(K60,LEN(K60)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
       <c r="R60" s="3"/>
       <c r="T60" s="7" t="str">
         <f>$B$16</f>
@@ -5776,12 +5776,12 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
-      <c r="X60" s="22" t="str">
+      <c r="X60" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET(#REF!,(INT(ROW(Y57)/22)*3)+((COLUMN(Y57)+2)/9),MATCH(RIGHT(T60,LEN(T60)-1),#REF!,0))="","",OFFSET(#REF!,(INT(ROW(Y57)/22)*3)+((COLUMN(Y57)+2)/9),MATCH(RIGHT(T60,LEN(T60)-1),#REF!,0))),"")</f>
         <v/>
       </c>
-      <c r="Y60" s="22"/>
-      <c r="Z60" s="22"/>
+      <c r="Y60" s="21"/>
+      <c r="Z60" s="21"/>
       <c r="AA60" s="3"/>
     </row>
     <row r="61" spans="2:27" ht="7.5" customHeight="1">
@@ -5845,12 +5845,12 @@
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
-      <c r="F63" s="21" t="s">
+      <c r="F63" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
       <c r="J63" s="3"/>
       <c r="K63" s="20" t="s">
         <v>17</v>
@@ -5858,54 +5858,54 @@
       <c r="L63" s="20"/>
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
-      <c r="O63" s="21" t="s">
+      <c r="O63" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
+      <c r="P63" s="19"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="19"/>
       <c r="T63" s="20" t="s">
         <v>17</v>
       </c>
       <c r="U63" s="20"/>
       <c r="V63" s="20"/>
       <c r="W63" s="20"/>
-      <c r="X63" s="21" t="s">
+      <c r="X63" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Y63" s="21"/>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="21"/>
+      <c r="Y63" s="19"/>
+      <c r="Z63" s="19"/>
+      <c r="AA63" s="19"/>
     </row>
     <row r="64" spans="2:27" ht="16.5" customHeight="1">
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="18" t="s">
+      <c r="K64" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
       <c r="R64" s="3"/>
-      <c r="T64" s="18" t="s">
+      <c r="T64" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="U64" s="18"/>
-      <c r="V64" s="18"/>
-      <c r="W64" s="18"/>
-      <c r="X64" s="18"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
       <c r="AA64" s="3"/>
@@ -5915,64 +5915,64 @@
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="O65" s="6"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
       <c r="V65" s="6"/>
       <c r="X65" s="6"/>
-      <c r="Y65" s="19"/>
-      <c r="Z65" s="19"/>
-      <c r="AA65" s="19"/>
+      <c r="Y65" s="18"/>
+      <c r="Z65" s="18"/>
+      <c r="AA65" s="18"/>
     </row>
     <row r="66" spans="1:28">
-      <c r="B66" s="16" t="str">
+      <c r="B66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="F66" s="17" t="str">
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
+      <c r="F66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="K66" s="16" t="str">
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="K66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="O66" s="17" t="str">
+      <c r="L66" s="23"/>
+      <c r="M66" s="23"/>
+      <c r="O66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="T66" s="16" t="str">
+      <c r="P66" s="24"/>
+      <c r="Q66" s="24"/>
+      <c r="R66" s="24"/>
+      <c r="T66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
-      <c r="X66" s="17" t="str">
+      <c r="U66" s="23"/>
+      <c r="V66" s="23"/>
+      <c r="X66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y66" s="17"/>
-      <c r="Z66" s="17"/>
-      <c r="AA66" s="17"/>
+      <c r="Y66" s="24"/>
+      <c r="Z66" s="24"/>
+      <c r="AA66" s="24"/>
     </row>
     <row r="67" spans="1:28" ht="3.75" customHeight="1">
       <c r="A67" t="s">
@@ -5990,6 +5990,126 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="X8:Z8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="X10:Z10"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="X22:AA22"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="K20:O20"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="X31:Z31"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="X33:Z33"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="O44:R44"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="O53:Q53"/>
+    <mergeCell ref="X53:Z53"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="Y43:AA43"/>
+    <mergeCell ref="X44:AA44"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="O52:Q52"/>
+    <mergeCell ref="X52:Z52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="O50:Q50"/>
+    <mergeCell ref="X50:Z50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="O66:R66"/>
+    <mergeCell ref="T66:V66"/>
+    <mergeCell ref="X66:AA66"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="O57:Q57"/>
+    <mergeCell ref="X57:Z57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="O58:Q58"/>
+    <mergeCell ref="X58:Z58"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="O59:Q59"/>
+    <mergeCell ref="X59:Z59"/>
+    <mergeCell ref="X60:Z60"/>
+    <mergeCell ref="O60:Q60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="O56:Q56"/>
+    <mergeCell ref="X56:Z56"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="X55:Z55"/>
+    <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="P65:R65"/>
+    <mergeCell ref="Y65:AA65"/>
+    <mergeCell ref="T64:X64"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="X6:Z6"/>
@@ -6014,126 +6134,6 @@
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="O54:Q54"/>
     <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="O56:Q56"/>
-    <mergeCell ref="X56:Z56"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="X55:Z55"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="P65:R65"/>
-    <mergeCell ref="Y65:AA65"/>
-    <mergeCell ref="T64:X64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="O66:R66"/>
-    <mergeCell ref="T66:V66"/>
-    <mergeCell ref="X66:AA66"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="O57:Q57"/>
-    <mergeCell ref="X57:Z57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="O58:Q58"/>
-    <mergeCell ref="X58:Z58"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="O59:Q59"/>
-    <mergeCell ref="X59:Z59"/>
-    <mergeCell ref="X60:Z60"/>
-    <mergeCell ref="O60:Q60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="O53:Q53"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="Y43:AA43"/>
-    <mergeCell ref="X44:AA44"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="O52:Q52"/>
-    <mergeCell ref="X52:Z52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="O50:Q50"/>
-    <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="O44:R44"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="X35:Z35"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="X34:Z34"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="X33:Z33"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="X31:Z31"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="X22:AA22"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="K20:O20"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="X10:Z10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6145,33 +6145,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C07CF2-022B-45F5-BE30-2881F0C24896}">
   <dimension ref="A1:BR67"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="0.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="2.6640625" customWidth="1"/>
-    <col min="4" max="4" width="2.33203125" customWidth="1"/>
-    <col min="5" max="5" width="1.21875" customWidth="1"/>
-    <col min="6" max="6" width="2.44140625" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" customWidth="1"/>
-    <col min="9" max="9" width="3.44140625" customWidth="1"/>
-    <col min="10" max="10" width="0.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" customWidth="1"/>
-    <col min="14" max="14" width="1.21875" customWidth="1"/>
-    <col min="15" max="15" width="2.44140625" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" customWidth="1"/>
-    <col min="18" max="18" width="3.21875" customWidth="1"/>
-    <col min="19" max="19" width="0.88671875" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" customWidth="1"/>
-    <col min="21" max="21" width="2.6640625" customWidth="1"/>
-    <col min="22" max="22" width="2.33203125" customWidth="1"/>
-    <col min="23" max="23" width="1.21875" customWidth="1"/>
-    <col min="24" max="24" width="2.44140625" customWidth="1"/>
-    <col min="26" max="26" width="4.6640625" customWidth="1"/>
-    <col min="27" max="27" width="3.21875" customWidth="1"/>
-    <col min="32" max="32" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.875" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="2.625" customWidth="1"/>
+    <col min="4" max="4" width="2.375" customWidth="1"/>
+    <col min="5" max="5" width="1.25" customWidth="1"/>
+    <col min="6" max="6" width="2.5" customWidth="1"/>
+    <col min="8" max="8" width="4.625" customWidth="1"/>
+    <col min="9" max="9" width="3.5" customWidth="1"/>
+    <col min="10" max="10" width="0.875" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="2.625" customWidth="1"/>
+    <col min="13" max="13" width="2.375" customWidth="1"/>
+    <col min="14" max="14" width="1.25" customWidth="1"/>
+    <col min="15" max="15" width="2.5" customWidth="1"/>
+    <col min="17" max="17" width="4.625" customWidth="1"/>
+    <col min="18" max="18" width="3.25" customWidth="1"/>
+    <col min="19" max="19" width="0.875" customWidth="1"/>
+    <col min="20" max="20" width="14.625" customWidth="1"/>
+    <col min="21" max="21" width="2.625" customWidth="1"/>
+    <col min="22" max="22" width="2.375" customWidth="1"/>
+    <col min="23" max="23" width="1.25" customWidth="1"/>
+    <col min="24" max="24" width="2.5" customWidth="1"/>
+    <col min="26" max="26" width="4.625" customWidth="1"/>
+    <col min="27" max="27" width="3.25" customWidth="1"/>
+    <col min="32" max="32" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="3.75" customHeight="1">
@@ -6195,31 +6195,31 @@
         <v>13</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
       <c r="K6" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L6" s="9"/>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
       <c r="T6" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U6" s="9"/>
-      <c r="X6" s="19" t="s">
+      <c r="X6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="18"/>
     </row>
     <row r="7" spans="1:32">
       <c r="B7" s="1" t="s">
@@ -6271,11 +6271,11 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>100.181868238294</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="7" t="str">
@@ -6285,11 +6285,11 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="22">
+      <c r="O8" s="21">
         <v>97.458565610919905</v>
       </c>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
       <c r="R8" s="3"/>
       <c r="T8" s="7" t="str">
         <f>$B$8</f>
@@ -6298,11 +6298,11 @@
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
-      <c r="X8" s="22">
+      <c r="X8" s="21">
         <v>99.494383077133705</v>
       </c>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:32" ht="22.5" customHeight="1">
@@ -6312,11 +6312,11 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>107.8070670255</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="7" t="str">
@@ -6326,11 +6326,11 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="22">
+      <c r="O9" s="21">
         <v>107.0100681755</v>
       </c>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
       <c r="R9" s="3"/>
       <c r="T9" s="7" t="str">
         <f>$B$9</f>
@@ -6339,11 +6339,11 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="22">
+      <c r="X9" s="21">
         <v>105.60356591350001</v>
       </c>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:32" ht="22.5" customHeight="1">
@@ -6353,11 +6353,11 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>100.40757768598399</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="7" t="str">
@@ -6367,11 +6367,11 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="22">
+      <c r="O10" s="21">
         <v>99.216280119785097</v>
       </c>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
       <c r="R10" s="3"/>
       <c r="T10" s="7" t="str">
         <f>$B$10</f>
@@ -6380,11 +6380,11 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
-      <c r="X10" s="22">
+      <c r="X10" s="21">
         <v>98.602425860730705</v>
       </c>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
       <c r="AA10" s="3"/>
     </row>
     <row r="11" spans="1:32" ht="22.5" customHeight="1">
@@ -6394,11 +6394,11 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <v>98.299113978363707</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="7" t="str">
@@ -6408,11 +6408,11 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="22">
+      <c r="O11" s="21">
         <v>97.503602672535706</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
       <c r="R11" s="3"/>
       <c r="T11" s="7" t="str">
         <f>$B$11</f>
@@ -6421,11 +6421,11 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
-      <c r="X11" s="22">
+      <c r="X11" s="21">
         <v>96.371444600606594</v>
       </c>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:32" ht="22.5" customHeight="1">
@@ -6435,11 +6435,11 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>101.958743013697</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="7" t="str">
@@ -6449,11 +6449,11 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="22">
+      <c r="O12" s="21">
         <v>101.04043067446401</v>
       </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
       <c r="R12" s="3"/>
       <c r="T12" s="7" t="str">
         <f>$B$12</f>
@@ -6462,11 +6462,11 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="22">
+      <c r="X12" s="21">
         <v>99.993501083123803</v>
       </c>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
       <c r="AA12" s="3"/>
     </row>
     <row r="13" spans="1:32" ht="22.5" customHeight="1">
@@ -6476,11 +6476,11 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>96.907010068370596</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="7" t="str">
@@ -6490,11 +6490,11 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="22">
+      <c r="O13" s="21">
         <v>96.282316557771594</v>
       </c>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
       <c r="R13" s="3"/>
       <c r="T13" s="7" t="str">
         <f>$B$13</f>
@@ -6503,11 +6503,11 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
-      <c r="X13" s="22">
+      <c r="X13" s="21">
         <v>94.997406774159799</v>
       </c>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:32" ht="22.5" customHeight="1">
@@ -6517,11 +6517,11 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <v>102.80414661488101</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="7" t="str">
@@ -6531,11 +6531,11 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="O14" s="22">
+      <c r="O14" s="21">
         <v>101.389554272289</v>
       </c>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
       <c r="R14" s="3"/>
       <c r="T14" s="7" t="str">
         <f>$B$14</f>
@@ -6544,11 +6544,11 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
-      <c r="X14" s="22">
+      <c r="X14" s="21">
         <v>99.648043416711403</v>
       </c>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="22"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
       <c r="AA14" s="3"/>
       <c r="AF14" s="11"/>
     </row>
@@ -6559,11 +6559,11 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>103.487400613959</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="7" t="str">
@@ -6573,11 +6573,11 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="22">
+      <c r="O15" s="21">
         <v>102.009617511521</v>
       </c>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
       <c r="R15" s="3"/>
       <c r="T15" s="7" t="str">
         <f>$B$15</f>
@@ -6586,11 +6586,11 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
-      <c r="X15" s="22">
+      <c r="X15" s="21">
         <v>101.27445812728</v>
       </c>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:32" ht="22.5" customHeight="1">
@@ -6600,11 +6600,11 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>99.629560892360402</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="7" t="str">
@@ -6614,11 +6614,11 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
-      <c r="O16" s="22">
+      <c r="O16" s="21">
         <v>96.207803207510807</v>
       </c>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
       <c r="R16" s="3"/>
       <c r="T16" s="7" t="str">
         <f>$B$16</f>
@@ -6627,11 +6627,11 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
-      <c r="X16" s="22">
+      <c r="X16" s="21">
         <v>97.7038129005619</v>
       </c>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:28" ht="7.5" customHeight="1">
@@ -6695,12 +6695,12 @@
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="3"/>
       <c r="K19" s="20" t="s">
         <v>16</v>
@@ -6708,54 +6708,54 @@
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
-      <c r="O19" s="21" t="s">
+      <c r="O19" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
       <c r="T19" s="20" t="s">
         <v>16</v>
       </c>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
-      <c r="X19" s="21" t="s">
+      <c r="X19" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:28" ht="16.5" customHeight="1">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
-      <c r="T20" s="18" t="s">
+      <c r="T20" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
       <c r="AA20" s="3"/>
@@ -6765,62 +6765,62 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="F21" s="6"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="O21" s="6"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="X21" s="6"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="F22" s="17" t="s">
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="F22" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="K22" s="16" t="str">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="K22" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="O22" s="17" t="str">
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="O22" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="T22" s="16" t="str">
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="T22" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="X22" s="17" t="str">
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="X22" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
     </row>
     <row r="23" spans="1:28" ht="3.75" customHeight="1">
       <c r="A23" t="s">
@@ -6844,31 +6844,31 @@
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="C28" s="9"/>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
       <c r="K28" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L28" s="9"/>
-      <c r="O28" s="19" t="s">
+      <c r="O28" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
       <c r="T28" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U28" s="9"/>
-      <c r="X28" s="19" t="s">
+      <c r="X28" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
     </row>
     <row r="29" spans="1:28">
       <c r="B29" s="1" t="str">
@@ -6923,11 +6923,11 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="22">
+      <c r="F30" s="21">
         <v>97.031525017988997</v>
       </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="7" t="str">
@@ -6937,11 +6937,11 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="22">
+      <c r="O30" s="21">
         <v>97.804102007427204</v>
       </c>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
       <c r="R30" s="3"/>
       <c r="T30" s="7" t="str">
         <f>$B$8</f>
@@ -6950,11 +6950,11 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
-      <c r="X30" s="22">
+      <c r="X30" s="21">
         <v>99.026887790332495</v>
       </c>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
+      <c r="Y30" s="21"/>
+      <c r="Z30" s="21"/>
       <c r="AA30" s="3"/>
     </row>
     <row r="31" spans="1:28" ht="22.5" customHeight="1">
@@ -6965,11 +6965,11 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="22">
+      <c r="F31" s="21">
         <v>109.7040671365</v>
       </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="7" t="str">
@@ -6979,11 +6979,11 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-      <c r="O31" s="22">
+      <c r="O31" s="21">
         <v>106.6585660695</v>
       </c>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="22"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
       <c r="R31" s="3"/>
       <c r="T31" s="7" t="str">
         <f>$B$9</f>
@@ -6992,11 +6992,11 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
-      <c r="X31" s="22">
+      <c r="X31" s="21">
         <v>109.5900657875</v>
       </c>
-      <c r="Y31" s="22"/>
-      <c r="Z31" s="22"/>
+      <c r="Y31" s="21"/>
+      <c r="Z31" s="21"/>
       <c r="AA31" s="3"/>
       <c r="AB31" t="s">
         <v>14</v>
@@ -7010,11 +7010,11 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <v>99.318255230386697</v>
       </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="7" t="str">
@@ -7024,11 +7024,11 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-      <c r="O32" s="22">
+      <c r="O32" s="21">
         <v>99.0200573032226</v>
       </c>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
       <c r="R32" s="3"/>
       <c r="T32" s="7" t="str">
         <f>$B$10</f>
@@ -7037,11 +7037,11 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
-      <c r="X32" s="22">
+      <c r="X32" s="21">
         <v>101.000798490208</v>
       </c>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="21"/>
       <c r="AA32" s="3"/>
     </row>
     <row r="33" spans="1:70" ht="22.5" customHeight="1">
@@ -7052,11 +7052,11 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="22">
+      <c r="F33" s="21">
         <v>94.797780271157094</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="7" t="str">
@@ -7066,11 +7066,11 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="22">
+      <c r="O33" s="21">
         <v>95.365060145022596</v>
       </c>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
       <c r="R33" s="3"/>
       <c r="T33" s="7" t="str">
         <f>$B$11</f>
@@ -7079,11 +7079,11 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
-      <c r="X33" s="22">
+      <c r="X33" s="21">
         <v>97.312130073336505</v>
       </c>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="22"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="21"/>
       <c r="AA33" s="3"/>
     </row>
     <row r="34" spans="1:70" ht="22.5" customHeight="1">
@@ -7094,11 +7094,11 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="22">
+      <c r="F34" s="21">
         <v>97.948038875785699</v>
       </c>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="7" t="str">
@@ -7108,11 +7108,11 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-      <c r="O34" s="22">
+      <c r="O34" s="21">
         <v>98.834756933806602</v>
       </c>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
       <c r="R34" s="3"/>
       <c r="T34" s="7" t="str">
         <f>$B$12</f>
@@ -7121,11 +7121,11 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
-      <c r="X34" s="22">
+      <c r="X34" s="21">
         <v>101.07404364837799</v>
       </c>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
+      <c r="Y34" s="21"/>
+      <c r="Z34" s="21"/>
       <c r="AA34" s="3"/>
       <c r="AF34" s="12"/>
       <c r="AG34" s="13"/>
@@ -7175,11 +7175,11 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="22">
+      <c r="F35" s="21">
         <v>93.180259460310296</v>
       </c>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="7" t="str">
@@ -7189,11 +7189,11 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-      <c r="O35" s="22">
+      <c r="O35" s="21">
         <v>93.713708964234002</v>
       </c>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
       <c r="R35" s="3"/>
       <c r="T35" s="7" t="str">
         <f>$B$13</f>
@@ -7202,11 +7202,11 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
-      <c r="X35" s="22">
+      <c r="X35" s="21">
         <v>96.057426088365503</v>
       </c>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="21"/>
       <c r="AA35" s="3"/>
       <c r="AF35" s="12"/>
       <c r="AG35" s="13"/>
@@ -7256,11 +7256,11 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="22">
+      <c r="F36" s="21">
         <v>98.6456062747517</v>
       </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="7" t="str">
@@ -7270,11 +7270,11 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-      <c r="O36" s="22">
+      <c r="O36" s="21">
         <v>98.057265624134601</v>
       </c>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
       <c r="R36" s="3"/>
       <c r="T36" s="7" t="str">
         <f>$B$14</f>
@@ -7283,11 +7283,11 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
-      <c r="X36" s="22">
+      <c r="X36" s="21">
         <v>101.419940409418</v>
       </c>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
       <c r="AA36" s="3"/>
     </row>
     <row r="37" spans="1:70" ht="22.5" customHeight="1">
@@ -7298,11 +7298,11 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="22">
+      <c r="F37" s="21">
         <v>100.714369898556</v>
       </c>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="7" t="str">
@@ -7312,11 +7312,11 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-      <c r="O37" s="22">
+      <c r="O37" s="21">
         <v>100.06680946054399</v>
       </c>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="21"/>
       <c r="R37" s="3"/>
       <c r="T37" s="7" t="str">
         <f>$B$15</f>
@@ -7325,11 +7325,11 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
-      <c r="X37" s="22">
+      <c r="X37" s="21">
         <v>103.649648880987</v>
       </c>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="22"/>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="21"/>
       <c r="AA37" s="3"/>
     </row>
     <row r="38" spans="1:70" ht="22.5" customHeight="1">
@@ -7340,11 +7340,11 @@
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="22">
+      <c r="F38" s="21">
         <v>98.3763987949701</v>
       </c>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="7" t="str">
@@ -7354,11 +7354,11 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-      <c r="O38" s="22">
+      <c r="O38" s="21">
         <v>96.173970793752105</v>
       </c>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
       <c r="R38" s="3"/>
       <c r="T38" s="7" t="str">
         <f>$B$16</f>
@@ -7367,11 +7367,11 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
-      <c r="X38" s="22">
+      <c r="X38" s="21">
         <v>101.037638487332</v>
       </c>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="21"/>
       <c r="AA38" s="3"/>
     </row>
     <row r="39" spans="1:70" ht="7.5" customHeight="1">
@@ -7435,12 +7435,12 @@
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
       <c r="J41" s="3"/>
       <c r="K41" s="20" t="s">
         <v>16</v>
@@ -7448,54 +7448,54 @@
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
-      <c r="O41" s="21" t="s">
+      <c r="O41" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="21"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
       <c r="T41" s="20" t="s">
         <v>16</v>
       </c>
       <c r="U41" s="20"/>
       <c r="V41" s="20"/>
       <c r="W41" s="20"/>
-      <c r="X41" s="21" t="s">
+      <c r="X41" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="Y41" s="21"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="21"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="19"/>
     </row>
     <row r="42" spans="1:70" ht="16.5" customHeight="1">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="3"/>
-      <c r="T42" s="18" t="s">
+      <c r="T42" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="22"/>
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
       <c r="AA42" s="3"/>
@@ -7505,64 +7505,64 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="F43" s="6"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="O43" s="6"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
       <c r="T43" s="6"/>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
       <c r="X43" s="6"/>
-      <c r="Y43" s="19"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43" s="19"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
     </row>
     <row r="44" spans="1:70">
-      <c r="B44" s="16" t="str">
+      <c r="B44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="F44" s="17" t="str">
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="F44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="K44" s="16" t="str">
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="K44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="O44" s="17" t="str">
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="O44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="T44" s="16" t="str">
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="T44" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="X44" s="17" t="str">
+      <c r="U44" s="23"/>
+      <c r="V44" s="23"/>
+      <c r="X44" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
-      <c r="AA44" s="17"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
     </row>
     <row r="45" spans="1:70" ht="3" customHeight="1">
       <c r="A45" t="s">
@@ -7586,33 +7586,33 @@
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="C50" s="9"/>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
       <c r="K50" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="L50" s="9"/>
-      <c r="O50" s="19" t="str">
+      <c r="O50" s="18" t="e">
         <f ca="1">IF(OFFSET([1]autofill!$B$2,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),0)="","",OFFSET([1]autofill!$B$2,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),0))</f>
-        <v/>
-      </c>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
       <c r="T50" s="9" t="str">
         <f>$B$6</f>
         <v xml:space="preserve">NF-SEMI STD  : </v>
       </c>
       <c r="U50" s="9"/>
-      <c r="X50" s="19" t="str">
+      <c r="X50" s="18" t="e">
         <f ca="1">IF(OFFSET([1]autofill!$B$2,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),0)="","",OFFSET([1]autofill!$B$2,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),0))</f>
-        <v/>
-      </c>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="18"/>
     </row>
     <row r="51" spans="2:27">
       <c r="B51" s="1" t="str">
@@ -7667,11 +7667,11 @@
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="22">
+      <c r="F52" s="21">
         <v>99.319481956289394</v>
       </c>
-      <c r="G52" s="22"/>
-      <c r="H52" s="22"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="7" t="str">
@@ -7681,12 +7681,12 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
-      <c r="O52" s="22" t="str">
+      <c r="O52" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P49)/22)*3)+((COLUMN(P49)+2)/9),MATCH(RIGHT(K52,LEN(K52)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P49)/22)*3)+((COLUMN(P49)+2)/9),MATCH(RIGHT(K52,LEN(K52)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
+      <c r="P52" s="21"/>
+      <c r="Q52" s="21"/>
       <c r="R52" s="3"/>
       <c r="T52" s="7" t="str">
         <f>$B$8</f>
@@ -7695,12 +7695,12 @@
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
-      <c r="X52" s="22" t="str">
+      <c r="X52" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y49)/22)*3)+((COLUMN(Y49)+2)/9),MATCH(RIGHT(T52,LEN(T52)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y49)/22)*3)+((COLUMN(Y49)+2)/9),MATCH(RIGHT(T52,LEN(T52)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y52" s="22"/>
-      <c r="Z52" s="22"/>
+      <c r="Y52" s="21"/>
+      <c r="Z52" s="21"/>
       <c r="AA52" s="3"/>
     </row>
     <row r="53" spans="2:27" ht="22.5" customHeight="1">
@@ -7711,11 +7711,11 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="22">
+      <c r="F53" s="21">
         <v>106.499565289</v>
       </c>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="7" t="str">
@@ -7725,12 +7725,12 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-      <c r="O53" s="22" t="str">
+      <c r="O53" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),MATCH(RIGHT(K53,LEN(K53)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P50)/22)*3)+((COLUMN(P50)+2)/9),MATCH(RIGHT(K53,LEN(K53)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
+      <c r="P53" s="21"/>
+      <c r="Q53" s="21"/>
       <c r="R53" s="3"/>
       <c r="T53" s="7" t="str">
         <f>$B$9</f>
@@ -7739,12 +7739,12 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
-      <c r="X53" s="22" t="str">
+      <c r="X53" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),MATCH(RIGHT(T53,LEN(T53)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y50)/22)*3)+((COLUMN(Y50)+2)/9),MATCH(RIGHT(T53,LEN(T53)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y53" s="22"/>
-      <c r="Z53" s="22"/>
+      <c r="Y53" s="21"/>
+      <c r="Z53" s="21"/>
       <c r="AA53" s="3"/>
     </row>
     <row r="54" spans="2:27" ht="22.5" customHeight="1">
@@ -7755,11 +7755,11 @@
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="22">
+      <c r="F54" s="21">
         <v>101.57133101167901</v>
       </c>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="7" t="str">
@@ -7769,12 +7769,12 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
-      <c r="O54" s="22" t="str">
+      <c r="O54" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P51)/22)*3)+((COLUMN(P51)+2)/9),MATCH(RIGHT(K54,LEN(K54)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P51)/22)*3)+((COLUMN(P51)+2)/9),MATCH(RIGHT(K54,LEN(K54)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
       <c r="R54" s="3"/>
       <c r="T54" s="7" t="str">
         <f>$B$10</f>
@@ -7783,12 +7783,12 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
-      <c r="X54" s="22" t="str">
+      <c r="X54" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y51)/22)*3)+((COLUMN(Y51)+2)/9),MATCH(RIGHT(T54,LEN(T54)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y51)/22)*3)+((COLUMN(Y51)+2)/9),MATCH(RIGHT(T54,LEN(T54)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y54" s="22"/>
-      <c r="Z54" s="22"/>
+      <c r="Y54" s="21"/>
+      <c r="Z54" s="21"/>
       <c r="AA54" s="3"/>
     </row>
     <row r="55" spans="2:27" ht="22.5" customHeight="1">
@@ -7799,11 +7799,11 @@
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="22">
+      <c r="F55" s="21">
         <v>97.874269432546797</v>
       </c>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="7" t="str">
@@ -7813,12 +7813,12 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="O55" s="22" t="str">
+      <c r="O55" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P52)/22)*3)+((COLUMN(P52)+2)/9),MATCH(RIGHT(K55,LEN(K55)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P52)/22)*3)+((COLUMN(P52)+2)/9),MATCH(RIGHT(K55,LEN(K55)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
       <c r="R55" s="3"/>
       <c r="T55" s="7" t="str">
         <f>$B$11</f>
@@ -7827,12 +7827,12 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
-      <c r="X55" s="22" t="str">
+      <c r="X55" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y52)/22)*3)+((COLUMN(Y52)+2)/9),MATCH(RIGHT(T55,LEN(T55)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y52)/22)*3)+((COLUMN(Y52)+2)/9),MATCH(RIGHT(T55,LEN(T55)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y55" s="22"/>
-      <c r="Z55" s="22"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="21"/>
       <c r="AA55" s="3"/>
     </row>
     <row r="56" spans="2:27" ht="22.5" customHeight="1">
@@ -7843,11 +7843,11 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="22">
+      <c r="F56" s="21">
         <v>100.60819194851101</v>
       </c>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="7" t="str">
@@ -7857,12 +7857,12 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-      <c r="O56" s="22" t="str">
+      <c r="O56" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P53)/22)*3)+((COLUMN(P53)+2)/9),MATCH(RIGHT(K56,LEN(K56)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P53)/22)*3)+((COLUMN(P53)+2)/9),MATCH(RIGHT(K56,LEN(K56)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P56" s="22"/>
-      <c r="Q56" s="22"/>
+      <c r="P56" s="21"/>
+      <c r="Q56" s="21"/>
       <c r="R56" s="3"/>
       <c r="T56" s="7" t="str">
         <f>$B$12</f>
@@ -7871,12 +7871,12 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
-      <c r="X56" s="22" t="str">
+      <c r="X56" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y53)/22)*3)+((COLUMN(Y53)+2)/9),MATCH(RIGHT(T56,LEN(T56)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y53)/22)*3)+((COLUMN(Y53)+2)/9),MATCH(RIGHT(T56,LEN(T56)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y56" s="22"/>
-      <c r="Z56" s="22"/>
+      <c r="Y56" s="21"/>
+      <c r="Z56" s="21"/>
       <c r="AA56" s="3"/>
     </row>
     <row r="57" spans="2:27" ht="22.5" customHeight="1">
@@ -7887,11 +7887,11 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="22">
+      <c r="F57" s="21">
         <v>95.348016115001599</v>
       </c>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="7" t="str">
@@ -7901,12 +7901,12 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-      <c r="O57" s="22" t="str">
+      <c r="O57" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P54)/22)*3)+((COLUMN(P54)+2)/9),MATCH(RIGHT(K57,LEN(K57)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P54)/22)*3)+((COLUMN(P54)+2)/9),MATCH(RIGHT(K57,LEN(K57)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P57" s="22"/>
-      <c r="Q57" s="22"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="21"/>
       <c r="R57" s="3"/>
       <c r="T57" s="7" t="str">
         <f>$B$13</f>
@@ -7915,12 +7915,12 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
-      <c r="X57" s="22" t="str">
+      <c r="X57" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y54)/22)*3)+((COLUMN(Y54)+2)/9),MATCH(RIGHT(T57,LEN(T57)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y54)/22)*3)+((COLUMN(Y54)+2)/9),MATCH(RIGHT(T57,LEN(T57)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y57" s="22"/>
-      <c r="Z57" s="22"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="21"/>
       <c r="AA57" s="3"/>
     </row>
     <row r="58" spans="2:27" ht="22.5" customHeight="1">
@@ -7931,11 +7931,11 @@
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="22">
+      <c r="F58" s="21">
         <v>101.749157521447</v>
       </c>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="7" t="str">
@@ -7945,12 +7945,12 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
-      <c r="O58" s="22" t="str">
+      <c r="O58" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P55)/22)*3)+((COLUMN(P55)+2)/9),MATCH(RIGHT(K58,LEN(K58)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P55)/22)*3)+((COLUMN(P55)+2)/9),MATCH(RIGHT(K58,LEN(K58)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="22"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="21"/>
       <c r="R58" s="3"/>
       <c r="T58" s="7" t="str">
         <f>$B$14</f>
@@ -7959,12 +7959,12 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
-      <c r="X58" s="22" t="str">
+      <c r="X58" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y55)/22)*3)+((COLUMN(Y55)+2)/9),MATCH(RIGHT(T58,LEN(T58)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y55)/22)*3)+((COLUMN(Y55)+2)/9),MATCH(RIGHT(T58,LEN(T58)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y58" s="22"/>
-      <c r="Z58" s="22"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="21"/>
       <c r="AA58" s="3"/>
     </row>
     <row r="59" spans="2:27" ht="22.5" customHeight="1">
@@ -7975,11 +7975,11 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="22">
+      <c r="F59" s="21">
         <v>103.27518489478101</v>
       </c>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="7" t="str">
@@ -7989,12 +7989,12 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="O59" s="22" t="str">
+      <c r="O59" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P56)/22)*3)+((COLUMN(P56)+2)/9),MATCH(RIGHT(K59,LEN(K59)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P56)/22)*3)+((COLUMN(P56)+2)/9),MATCH(RIGHT(K59,LEN(K59)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="22"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
       <c r="R59" s="3"/>
       <c r="T59" s="7" t="str">
         <f>$B$15</f>
@@ -8003,12 +8003,12 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
-      <c r="X59" s="22" t="str">
+      <c r="X59" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y56)/22)*3)+((COLUMN(Y56)+2)/9),MATCH(RIGHT(T59,LEN(T59)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y56)/22)*3)+((COLUMN(Y56)+2)/9),MATCH(RIGHT(T59,LEN(T59)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y59" s="22"/>
-      <c r="Z59" s="22"/>
+      <c r="Y59" s="21"/>
+      <c r="Z59" s="21"/>
       <c r="AA59" s="3"/>
     </row>
     <row r="60" spans="2:27" ht="22.5" customHeight="1">
@@ -8019,11 +8019,11 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="22">
+      <c r="F60" s="21">
         <v>100.197675235278</v>
       </c>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="7" t="str">
@@ -8033,12 +8033,12 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-      <c r="O60" s="22" t="str">
+      <c r="O60" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(P57)/22)*3)+((COLUMN(P57)+2)/9),MATCH(RIGHT(K60,LEN(K60)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(P57)/22)*3)+((COLUMN(P57)+2)/9),MATCH(RIGHT(K60,LEN(K60)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
       <c r="R60" s="3"/>
       <c r="T60" s="7" t="str">
         <f>$B$16</f>
@@ -8047,12 +8047,12 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
-      <c r="X60" s="22" t="str">
+      <c r="X60" s="21" t="str">
         <f ca="1">IFERROR(IF(OFFSET([1]autofill!$G$2,(INT(ROW(Y57)/22)*3)+((COLUMN(Y57)+2)/9),MATCH(RIGHT(T60,LEN(T60)-1),[1]autofill!$H$2:$AT$2,0))="","",OFFSET([1]autofill!$G$2,(INT(ROW(Y57)/22)*3)+((COLUMN(Y57)+2)/9),MATCH(RIGHT(T60,LEN(T60)-1),[1]autofill!$H$2:$AT$2,0))),"")</f>
         <v/>
       </c>
-      <c r="Y60" s="22"/>
-      <c r="Z60" s="22"/>
+      <c r="Y60" s="21"/>
+      <c r="Z60" s="21"/>
       <c r="AA60" s="3"/>
     </row>
     <row r="61" spans="2:27" ht="7.5" customHeight="1">
@@ -8116,12 +8116,12 @@
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
-      <c r="F63" s="21" t="s">
+      <c r="F63" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
       <c r="J63" s="3"/>
       <c r="K63" s="20" t="s">
         <v>16</v>
@@ -8129,54 +8129,54 @@
       <c r="L63" s="20"/>
       <c r="M63" s="20"/>
       <c r="N63" s="20"/>
-      <c r="O63" s="21" t="s">
+      <c r="O63" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
+      <c r="P63" s="19"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="19"/>
       <c r="T63" s="20" t="s">
         <v>16</v>
       </c>
       <c r="U63" s="20"/>
       <c r="V63" s="20"/>
       <c r="W63" s="20"/>
-      <c r="X63" s="21" t="s">
+      <c r="X63" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Y63" s="21"/>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="21"/>
+      <c r="Y63" s="19"/>
+      <c r="Z63" s="19"/>
+      <c r="AA63" s="19"/>
     </row>
     <row r="64" spans="2:27" ht="16.5" customHeight="1">
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="18" t="s">
+      <c r="K64" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
       <c r="R64" s="3"/>
-      <c r="T64" s="18" t="s">
+      <c r="T64" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="U64" s="18"/>
-      <c r="V64" s="18"/>
-      <c r="W64" s="18"/>
-      <c r="X64" s="18"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
       <c r="AA64" s="3"/>
@@ -8186,64 +8186,64 @@
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="O65" s="6"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
       <c r="V65" s="6"/>
       <c r="X65" s="6"/>
-      <c r="Y65" s="19"/>
-      <c r="Z65" s="19"/>
-      <c r="AA65" s="19"/>
+      <c r="Y65" s="18"/>
+      <c r="Z65" s="18"/>
+      <c r="AA65" s="18"/>
     </row>
     <row r="66" spans="1:28">
-      <c r="B66" s="16" t="str">
+      <c r="B66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="F66" s="17" t="str">
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
+      <c r="F66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="K66" s="16" t="str">
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="K66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="O66" s="17" t="str">
+      <c r="L66" s="23"/>
+      <c r="M66" s="23"/>
+      <c r="O66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="T66" s="16" t="str">
+      <c r="P66" s="24"/>
+      <c r="Q66" s="24"/>
+      <c r="R66" s="24"/>
+      <c r="T66" s="23" t="str">
         <f>$B$22</f>
         <v>安裝Engineer  Signature  / Date</v>
       </c>
-      <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
-      <c r="X66" s="17" t="str">
+      <c r="U66" s="23"/>
+      <c r="V66" s="23"/>
+      <c r="X66" s="24" t="str">
         <f>$F$22</f>
         <v>Authorized Signature  / Date</v>
       </c>
-      <c r="Y66" s="17"/>
-      <c r="Z66" s="17"/>
-      <c r="AA66" s="17"/>
+      <c r="Y66" s="24"/>
+      <c r="Z66" s="24"/>
+      <c r="AA66" s="24"/>
     </row>
     <row r="67" spans="1:28" ht="3.75" customHeight="1">
       <c r="A67" t="s">
@@ -8261,6 +8261,138 @@
     </row>
   </sheetData>
   <mergeCells count="144">
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="O66:R66"/>
+    <mergeCell ref="T66:V66"/>
+    <mergeCell ref="X66:AA66"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="K64:O64"/>
+    <mergeCell ref="T64:X64"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="P65:R65"/>
+    <mergeCell ref="Y65:AA65"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="K63:N63"/>
+    <mergeCell ref="O63:R63"/>
+    <mergeCell ref="T63:W63"/>
+    <mergeCell ref="X63:AA63"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="O59:Q59"/>
+    <mergeCell ref="X59:Z59"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="O60:Q60"/>
+    <mergeCell ref="X60:Z60"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="O57:Q57"/>
+    <mergeCell ref="X57:Z57"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="O58:Q58"/>
+    <mergeCell ref="X58:Z58"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="O55:Q55"/>
+    <mergeCell ref="X55:Z55"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="O56:Q56"/>
+    <mergeCell ref="X56:Z56"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="O53:Q53"/>
+    <mergeCell ref="X53:Z53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="O54:Q54"/>
+    <mergeCell ref="X54:Z54"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="O50:Q50"/>
+    <mergeCell ref="X50:Z50"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="O52:Q52"/>
+    <mergeCell ref="X52:Z52"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="O44:R44"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="X44:AA44"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="Y43:AA43"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="K41:N41"/>
+    <mergeCell ref="O41:R41"/>
+    <mergeCell ref="T41:W41"/>
+    <mergeCell ref="X41:AA41"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="X33:Z33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="X31:Z31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="X22:AA22"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="K20:O20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="T19:W19"/>
+    <mergeCell ref="X19:AA19"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="X12:Z12"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="O9:Q9"/>
     <mergeCell ref="X9:Z9"/>
@@ -8273,138 +8405,6 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="O8:Q8"/>
     <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="T19:W19"/>
-    <mergeCell ref="X19:AA19"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="X22:AA22"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="K20:O20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="X31:Z31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="X35:Z35"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="X33:Z33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="X34:Z34"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="K41:N41"/>
-    <mergeCell ref="O41:R41"/>
-    <mergeCell ref="T41:W41"/>
-    <mergeCell ref="X41:AA41"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="O44:R44"/>
-    <mergeCell ref="T44:V44"/>
-    <mergeCell ref="X44:AA44"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="Y43:AA43"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="O53:Q53"/>
-    <mergeCell ref="X53:Z53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="O54:Q54"/>
-    <mergeCell ref="X54:Z54"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="O50:Q50"/>
-    <mergeCell ref="X50:Z50"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="O52:Q52"/>
-    <mergeCell ref="X52:Z52"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="O57:Q57"/>
-    <mergeCell ref="X57:Z57"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="O58:Q58"/>
-    <mergeCell ref="X58:Z58"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="O55:Q55"/>
-    <mergeCell ref="X55:Z55"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="O56:Q56"/>
-    <mergeCell ref="X56:Z56"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="K63:N63"/>
-    <mergeCell ref="O63:R63"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="X63:AA63"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="O59:Q59"/>
-    <mergeCell ref="X59:Z59"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="O60:Q60"/>
-    <mergeCell ref="X60:Z60"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="O66:R66"/>
-    <mergeCell ref="T66:V66"/>
-    <mergeCell ref="X66:AA66"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="K64:O64"/>
-    <mergeCell ref="T64:X64"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="P65:R65"/>
-    <mergeCell ref="Y65:AA65"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8416,114 +8416,114 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B22D81-EFDD-4EC2-8DD1-BE1C29059184}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="73.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" customWidth="1"/>
+    <col min="1" max="1" width="24.375" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="16" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="23"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="16" t="s">
         <v>65</v>
       </c>
     </row>
@@ -8534,12 +8534,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="322e9515-a834-43ab-8dfc-fb636c333c6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="31cd1f55-1d3a-455d-9509-84b6ef795acc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8778,20 +8780,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="322e9515-a834-43ab-8dfc-fb636c333c6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="31cd1f55-1d3a-455d-9509-84b6ef795acc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8914172F-6FCA-40EC-B1B5-9F8714A12C4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80BFDBD-EA38-4961-8006-E492C86800C2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="322e9515-a834-43ab-8dfc-fb636c333c6e"/>
+    <ds:schemaRef ds:uri="31cd1f55-1d3a-455d-9509-84b6ef795acc"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8816,12 +8819,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C80BFDBD-EA38-4961-8006-E492C86800C2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8914172F-6FCA-40EC-B1B5-9F8714A12C4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="322e9515-a834-43ab-8dfc-fb636c333c6e"/>
-    <ds:schemaRef ds:uri="31cd1f55-1d3a-455d-9509-84b6ef795acc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>